--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\88696\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kelly\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E72713E-2131-4245-BCF6-709D13B1CE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D86C878E-2457-4053-BDD1-0D2423A3D704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11265" yWindow="465" windowWidth="17460" windowHeight="14310" activeTab="1" xr2:uid="{9D40D978-2827-49F4-8C75-FCA4B471ABC7}"/>
+    <workbookView xWindow="8550" yWindow="0" windowWidth="15450" windowHeight="12615" firstSheet="1" activeTab="1" xr2:uid="{9D40D978-2827-49F4-8C75-FCA4B471ABC7}"/>
   </bookViews>
   <sheets>
-    <sheet name="台積電" sheetId="2" r:id="rId1"/>
-    <sheet name="鴻海" sheetId="3" r:id="rId2"/>
-    <sheet name="聯發科" sheetId="4" r:id="rId3"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="台積電" sheetId="2" r:id="rId2"/>
+    <sheet name="鴻海" sheetId="3" r:id="rId3"/>
+    <sheet name="聯發科" sheetId="4" r:id="rId4"/>
+    <sheet name="南亞科" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -29,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -41,7 +41,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="11">
+  <si>
+    <t>台積電2330</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>情緒分數</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,6 +59,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>鴻海2317</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聯發科2454</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -63,7 +75,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新聞全過期</t>
+    <t>新聞全過期 分數沿用上次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上漲預測(技術)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上漲預測(加情緒)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -71,7 +91,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -86,6 +106,13 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,11 +137,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -205,7 +241,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2788621005889519E-2"/>
+          <c:y val="8.0572533522920708E-2"/>
+          <c:w val="0.90000522621659362"/>
+          <c:h val="0.82229901477529965"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -249,10 +295,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>台積電!$A$2:$A$35</c:f>
+              <c:f>台積電!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46183</c:v>
                 </c:pt>
@@ -354,16 +400,127 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46283</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>台積電!$B$2:$B$35</c:f>
+              <c:f>台積電!$B$2:$B$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>64.930000000000007</c:v>
                 </c:pt>
@@ -465,6 +622,117 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>42.64</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>49.8</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>65.84</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>74.540000000000006</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>72.86</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>75.23</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>69.790000000000006</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>74.680000000000007</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>75.510000000000005</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>78.290000000000006</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>80.209999999999994</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>79.44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>77.58</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>87.42</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>71.89</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>59.68</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>62.22</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>64.92</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>56.87</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>61.54</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>72.61</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>81.12</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>85.27</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>70.94</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>73.55</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>63.28</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>68.02</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>72.290000000000006</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>90.35</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>84.39</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>83.36</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>72.59</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>64.69</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>57.58</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>50.51</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>56.63</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>70.8</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>82.27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -530,10 +798,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>台積電!$A$2:$A$35</c:f>
+              <c:f>台積電!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46183</c:v>
                 </c:pt>
@@ -635,16 +903,127 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46283</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>台積電!$C$2:$C$35</c:f>
+              <c:f>台積電!$C$2:$C$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>2255</c:v>
                 </c:pt>
@@ -746,6 +1125,117 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2205</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2425</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2370</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2320</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2405</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2365</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2370</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2380</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2395</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2415</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2435</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2395</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2380</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2350</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2375</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2410</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2375</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2415</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2410</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2405</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2440</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2385</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2390</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2410</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2460</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2470</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2465</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2450</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2410</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2380</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2385</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2380</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2425</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2460</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -896,7 +1386,7 @@
         <c:axId val="1095147839"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="1500"/>
+          <c:min val="2000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -1147,10 +1637,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>鴻海!$A$2:$A$35</c:f>
+              <c:f>鴻海!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46183</c:v>
                 </c:pt>
@@ -1252,16 +1742,127 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46283</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>鴻海!$B$2:$B$35</c:f>
+              <c:f>鴻海!$B$2:$B$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>51.16</c:v>
                 </c:pt>
@@ -1363,6 +1964,117 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>30.83</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>39.25</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>64.95</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>84.32</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>72.41</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>79.69</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>68.3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>75.19</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>88.66</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>85.26</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>83.07</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>83.9</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>81.38</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>85.12</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>75.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>69.64</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>69.28</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>71.27</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>76.77</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>72.58</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>74.75</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>79.66</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>83.53</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>74.08</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>73.95</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>67.239999999999995</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>73.510000000000005</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>74.45</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>84.16</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>83.36</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>79.849999999999994</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>71.150000000000006</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>64.58</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>55.87</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>45.84</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>51.81</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>67.63</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>82.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1428,10 +2140,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>鴻海!$A$2:$A$35</c:f>
+              <c:f>鴻海!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46183</c:v>
                 </c:pt>
@@ -1533,16 +2245,127 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46283</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>鴻海!$C$2:$C$35</c:f>
+              <c:f>鴻海!$C$2:$C$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>263</c:v>
                 </c:pt>
@@ -1644,6 +2467,117 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>237</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>229.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>250.5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>258.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>264.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>264.5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>263</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>259.5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>246.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>245.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>243.5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>246.5</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>247.5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>251.5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>248.5</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>246.5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>250.5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>250.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1795,7 +2729,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="280"/>
-          <c:min val="180"/>
+          <c:min val="190"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -2046,10 +2980,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>聯發科!$A$2:$A$35</c:f>
+              <c:f>聯發科!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46183</c:v>
                 </c:pt>
@@ -2151,16 +3085,127 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46283</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>聯發科!$B$2:$B$35</c:f>
+              <c:f>聯發科!$B$2:$B$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>63.21</c:v>
                 </c:pt>
@@ -2262,6 +3307,117 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>21.76</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>31.72</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>61.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>77.38</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>72.63</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>75.739999999999995</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>65.989999999999995</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>69.42</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>77.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>77.42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>78.56</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>79.48</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>77.680000000000007</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>77.8</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>71.010000000000005</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>57.71</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>58.78</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>60.1</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>64.06</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>63.79</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>71.23</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>77.8</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>81.44</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>56.8</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>69.680000000000007</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>57.4</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>63.02</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>66.760000000000005</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>89.68</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>84.58</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>82.97</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>70.010000000000005</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>56.84</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>50.13</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>60.9</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>70.75</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>84.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2327,10 +3483,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>聯發科!$A$2:$A$35</c:f>
+              <c:f>聯發科!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>46183</c:v>
                 </c:pt>
@@ -2432,16 +3588,127 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46283</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>聯發科!$C$2:$C$35</c:f>
+              <c:f>聯發科!$C$2:$C$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>4155</c:v>
                 </c:pt>
@@ -2543,6 +3810,117 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>3150</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3235</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3555</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3910</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3865</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3920</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3900</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4020</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4015</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4225</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4210</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4050</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3885</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3845</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3790</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3765</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3735</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3945</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3865</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3985</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3925</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4315</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>4275</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4340</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4415</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>4760</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4710</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>4625</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>4720</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4585</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4560</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4430</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4530</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4710</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2693,7 +4071,7 @@
         <c:axId val="1091439231"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="2000"/>
+          <c:min val="2900"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -2750,6 +4128,1072 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1091439231"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>南亞科</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>南亞科!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>情緒分數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>南亞科!$A$2:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>46218</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46219</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46220</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46223</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46224</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46225</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46226</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46227</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46230</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46231</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46283</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>南亞科!$B$2:$B$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>74.81</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75.28</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71.040000000000006</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67.92</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>75.27</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>77.89</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>77.86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>72.47</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>69.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>51.82</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>49.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>48.44</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>61.29</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>74.98</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>77.430000000000007</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>77.83</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>75.349999999999994</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>75.28</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>91.62</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>87.25</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>84.46</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>81.66</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>79.27</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>80.150000000000006</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>66.069999999999993</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>55.18</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>60.55</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>70.23</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>72.64</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>67.88</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>71.08</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>79.17</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>83.32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>70.83</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>70.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>75.44</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>69.98</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>72.040000000000006</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>87.24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>80.42</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>67.540000000000006</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>60.79</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>53.93</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>49.52</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>62.22</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>73.08</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>89.57</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0127-F24E-B3F5-1BD3D1119BE6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1266006463"/>
+        <c:axId val="1265998847"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>南亞科!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>收盤價</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>南亞科!$A$2:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>46218</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46219</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46220</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46223</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46224</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46225</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46226</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46227</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46230</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46231</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46283</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>南亞科!$C$2:$C$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>481</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>439</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>395.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>381</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>445.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>426</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>401</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>436</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>392.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>353.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>328</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>360.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>396.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>436</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>459</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>457</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>502</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>489</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>482.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>514</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>512</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>524</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>481</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>517</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>528</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>501</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>517</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>541</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>543</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>518</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>518</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>477.5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>496</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>517</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>531</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>523</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>493</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>473</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>465.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>492.5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>488</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>525</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0127-F24E-B3F5-1BD3D1119BE6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1328674207"/>
+        <c:axId val="831551647"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1266006463"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1265998847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1265998847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1266006463"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="831551647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="250"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1328674207"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1328674207"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="831551647"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2910,6 +5354,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4497,20 +6981,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>449842</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>88306</xdr:rowOff>
+      <xdr:colOff>440940</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>195129</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>807103</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>130561</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>531146</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>23739</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4583,15 +7583,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>206375</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>803275</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>41275</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4600,6 +7600,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41689946-F498-1BFD-191A-F13F315F9DA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{258709A5-1996-D71F-0C36-FA8FD94055E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4936,28 +7977,625 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147FB6CB-A0DD-4A3B-BD94-C57DC79FAD52}">
+  <dimension ref="A1:W17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.125" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B1" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C1" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D1" s="1">
+        <v>46185</v>
+      </c>
+      <c r="E1" s="1">
+        <v>46188</v>
+      </c>
+      <c r="F1" s="1">
+        <v>46189</v>
+      </c>
+      <c r="G1" s="1">
+        <v>46190</v>
+      </c>
+      <c r="H1" s="1">
+        <v>46191</v>
+      </c>
+      <c r="I1" s="1">
+        <v>46195</v>
+      </c>
+      <c r="J1" s="1">
+        <v>46196</v>
+      </c>
+      <c r="K1" s="1">
+        <v>46197</v>
+      </c>
+      <c r="L1" s="1">
+        <v>46198</v>
+      </c>
+      <c r="M1" s="1">
+        <v>46199</v>
+      </c>
+      <c r="N1" s="1">
+        <v>46202</v>
+      </c>
+      <c r="O1" s="1">
+        <v>46203</v>
+      </c>
+      <c r="P1" s="1">
+        <v>46204</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>46205</v>
+      </c>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>64.930000000000007</v>
+      </c>
+      <c r="C3">
+        <v>66.430000000000007</v>
+      </c>
+      <c r="D3">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="E3">
+        <v>89.76</v>
+      </c>
+      <c r="F3">
+        <v>93.55</v>
+      </c>
+      <c r="G3">
+        <v>87.4</v>
+      </c>
+      <c r="H3">
+        <v>84.57</v>
+      </c>
+      <c r="I3">
+        <v>84.43</v>
+      </c>
+      <c r="J3">
+        <v>77.09</v>
+      </c>
+      <c r="K3">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="L3">
+        <v>70.8</v>
+      </c>
+      <c r="M3">
+        <v>63.83</v>
+      </c>
+      <c r="N3">
+        <v>75.44</v>
+      </c>
+      <c r="O3">
+        <v>84.45</v>
+      </c>
+      <c r="P3">
+        <v>88.94</v>
+      </c>
+      <c r="Q3">
+        <v>84.61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2255</v>
+      </c>
+      <c r="C4">
+        <v>2250</v>
+      </c>
+      <c r="D4">
+        <v>2310</v>
+      </c>
+      <c r="E4">
+        <v>2375</v>
+      </c>
+      <c r="F4">
+        <v>2400</v>
+      </c>
+      <c r="G4">
+        <v>2385</v>
+      </c>
+      <c r="H4">
+        <v>2410</v>
+      </c>
+      <c r="I4">
+        <v>2510</v>
+      </c>
+      <c r="J4">
+        <v>2490</v>
+      </c>
+      <c r="K4">
+        <v>2390</v>
+      </c>
+      <c r="L4">
+        <v>2390</v>
+      </c>
+      <c r="M4">
+        <v>2340</v>
+      </c>
+      <c r="N4">
+        <v>2370</v>
+      </c>
+      <c r="O4">
+        <v>2410</v>
+      </c>
+      <c r="P4">
+        <v>2505</v>
+      </c>
+      <c r="Q4">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>54194</v>
+      </c>
+      <c r="C5">
+        <v>46418</v>
+      </c>
+      <c r="D5">
+        <v>26307</v>
+      </c>
+      <c r="E5">
+        <v>30229</v>
+      </c>
+      <c r="F5">
+        <v>37146</v>
+      </c>
+      <c r="G5">
+        <v>30059</v>
+      </c>
+      <c r="H5">
+        <v>49983</v>
+      </c>
+      <c r="I5">
+        <v>45208</v>
+      </c>
+      <c r="J5">
+        <v>39538</v>
+      </c>
+      <c r="K5">
+        <v>67304</v>
+      </c>
+      <c r="L5">
+        <v>41100</v>
+      </c>
+      <c r="M5">
+        <v>53800</v>
+      </c>
+      <c r="N5">
+        <v>38134</v>
+      </c>
+      <c r="O5">
+        <v>49540</v>
+      </c>
+      <c r="P5">
+        <v>37544</v>
+      </c>
+      <c r="Q5">
+        <v>35919</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>51.16</v>
+      </c>
+      <c r="C7">
+        <v>61.28</v>
+      </c>
+      <c r="D7">
+        <v>65.489999999999995</v>
+      </c>
+      <c r="E7">
+        <v>86.29</v>
+      </c>
+      <c r="F7">
+        <v>86.43</v>
+      </c>
+      <c r="G7">
+        <v>73.47</v>
+      </c>
+      <c r="H7">
+        <v>78.55</v>
+      </c>
+      <c r="I7">
+        <v>94.59</v>
+      </c>
+      <c r="J7">
+        <v>78.2</v>
+      </c>
+      <c r="K7">
+        <v>67.39</v>
+      </c>
+      <c r="L7">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="M7">
+        <v>58.05</v>
+      </c>
+      <c r="N7">
+        <v>68.03</v>
+      </c>
+      <c r="O7">
+        <v>79.33</v>
+      </c>
+      <c r="P7">
+        <v>85.52</v>
+      </c>
+      <c r="Q7">
+        <v>74.48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>263</v>
+      </c>
+      <c r="C8">
+        <v>258.5</v>
+      </c>
+      <c r="D8">
+        <v>260.5</v>
+      </c>
+      <c r="E8">
+        <v>267.5</v>
+      </c>
+      <c r="F8">
+        <v>269</v>
+      </c>
+      <c r="G8">
+        <v>272</v>
+      </c>
+      <c r="H8">
+        <v>268.5</v>
+      </c>
+      <c r="I8">
+        <v>268.5</v>
+      </c>
+      <c r="J8">
+        <v>259.5</v>
+      </c>
+      <c r="K8">
+        <v>256</v>
+      </c>
+      <c r="L8">
+        <v>257.5</v>
+      </c>
+      <c r="M8">
+        <v>248.5</v>
+      </c>
+      <c r="N8">
+        <v>246.5</v>
+      </c>
+      <c r="O8">
+        <v>251</v>
+      </c>
+      <c r="P8">
+        <v>248</v>
+      </c>
+      <c r="Q8">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>93369</v>
+      </c>
+      <c r="C9">
+        <v>97551</v>
+      </c>
+      <c r="D9">
+        <v>60261</v>
+      </c>
+      <c r="E9">
+        <v>54689</v>
+      </c>
+      <c r="F9">
+        <v>56879</v>
+      </c>
+      <c r="G9">
+        <v>42755</v>
+      </c>
+      <c r="H9">
+        <v>68997</v>
+      </c>
+      <c r="I9">
+        <v>67146</v>
+      </c>
+      <c r="J9">
+        <v>92064</v>
+      </c>
+      <c r="K9">
+        <v>63691</v>
+      </c>
+      <c r="L9">
+        <v>43578</v>
+      </c>
+      <c r="M9">
+        <v>80451</v>
+      </c>
+      <c r="N9">
+        <v>49210</v>
+      </c>
+      <c r="O9">
+        <v>52952</v>
+      </c>
+      <c r="P9">
+        <v>65881</v>
+      </c>
+      <c r="Q9">
+        <v>67897</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>63.21</v>
+      </c>
+      <c r="C11">
+        <v>67.72</v>
+      </c>
+      <c r="D11">
+        <v>66.3</v>
+      </c>
+      <c r="E11">
+        <v>88.06</v>
+      </c>
+      <c r="F11">
+        <v>88.29</v>
+      </c>
+      <c r="G11">
+        <v>80.58</v>
+      </c>
+      <c r="H11">
+        <v>80.13</v>
+      </c>
+      <c r="I11">
+        <v>94.19</v>
+      </c>
+      <c r="J11">
+        <v>79.87</v>
+      </c>
+      <c r="K11">
+        <v>68.64</v>
+      </c>
+      <c r="L11">
+        <v>66.31</v>
+      </c>
+      <c r="M11">
+        <v>61.87</v>
+      </c>
+      <c r="N11">
+        <v>69.47</v>
+      </c>
+      <c r="O11">
+        <v>79.95</v>
+      </c>
+      <c r="P11">
+        <v>85.94</v>
+      </c>
+      <c r="Q11">
+        <v>83.45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>4155</v>
+      </c>
+      <c r="C12">
+        <v>4085</v>
+      </c>
+      <c r="D12">
+        <v>4180</v>
+      </c>
+      <c r="E12">
+        <v>4470</v>
+      </c>
+      <c r="F12">
+        <v>4560</v>
+      </c>
+      <c r="G12">
+        <v>4460</v>
+      </c>
+      <c r="H12">
+        <v>4390</v>
+      </c>
+      <c r="I12">
+        <v>4465</v>
+      </c>
+      <c r="J12">
+        <v>4535</v>
+      </c>
+      <c r="K12">
+        <v>4285</v>
+      </c>
+      <c r="L12">
+        <v>4310</v>
+      </c>
+      <c r="M12">
+        <v>3880</v>
+      </c>
+      <c r="N12">
+        <v>3910</v>
+      </c>
+      <c r="O12">
+        <v>4245</v>
+      </c>
+      <c r="P12">
+        <v>4335</v>
+      </c>
+      <c r="Q12">
+        <v>43.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>17413</v>
+      </c>
+      <c r="C13">
+        <v>17557</v>
+      </c>
+      <c r="D13">
+        <v>8765</v>
+      </c>
+      <c r="E13">
+        <v>12015</v>
+      </c>
+      <c r="F13">
+        <v>11310</v>
+      </c>
+      <c r="G13">
+        <v>9198</v>
+      </c>
+      <c r="H13">
+        <v>12998</v>
+      </c>
+      <c r="I13">
+        <v>11596</v>
+      </c>
+      <c r="J13">
+        <v>18450</v>
+      </c>
+      <c r="K13">
+        <v>16421</v>
+      </c>
+      <c r="L13">
+        <v>10274</v>
+      </c>
+      <c r="M13">
+        <v>24916</v>
+      </c>
+      <c r="N13">
+        <v>11358</v>
+      </c>
+      <c r="O13">
+        <v>16095</v>
+      </c>
+      <c r="P13">
+        <v>10164</v>
+      </c>
+      <c r="Q13">
+        <v>8544</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>65.900000000000006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>101.95</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>76564</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53AD14CC-242E-6041-A559-1F3DEA9C60AF}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="21.125" customWidth="1"/>
+    <col min="5" max="5" width="13.625" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46183</v>
       </c>
@@ -4971,7 +8609,7 @@
         <v>54194</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46184</v>
       </c>
@@ -4985,7 +8623,7 @@
         <v>46418</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46185</v>
       </c>
@@ -4999,7 +8637,7 @@
         <v>26307</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46188</v>
       </c>
@@ -5013,7 +8651,7 @@
         <v>30229</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46189</v>
       </c>
@@ -5027,7 +8665,7 @@
         <v>37146</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46190</v>
       </c>
@@ -5041,7 +8679,7 @@
         <v>30059</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46191</v>
       </c>
@@ -5055,7 +8693,7 @@
         <v>49983</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46195</v>
       </c>
@@ -5069,7 +8707,7 @@
         <v>45208</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46196</v>
       </c>
@@ -5083,7 +8721,7 @@
         <v>39538</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46197</v>
       </c>
@@ -5097,7 +8735,7 @@
         <v>67304</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46198</v>
       </c>
@@ -5111,7 +8749,7 @@
         <v>41100</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46199</v>
       </c>
@@ -5125,7 +8763,7 @@
         <v>53800</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46202</v>
       </c>
@@ -5139,7 +8777,7 @@
         <v>38134</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46203</v>
       </c>
@@ -5153,7 +8791,7 @@
         <v>49540</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46204</v>
       </c>
@@ -5391,7 +9029,7 @@
         <v>24811</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46230</v>
       </c>
@@ -5405,10 +9043,10 @@
         <v>28939</v>
       </c>
       <c r="E33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46231</v>
       </c>
@@ -5422,7 +9060,7 @@
         <v>45333</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46232</v>
       </c>
@@ -5434,6 +9072,2002 @@
       </c>
       <c r="D35">
         <v>68140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B36">
+        <v>49.8</v>
+      </c>
+      <c r="C36">
+        <v>2205</v>
+      </c>
+      <c r="D36">
+        <v>51372</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B37">
+        <v>65.84</v>
+      </c>
+      <c r="C37">
+        <v>2425</v>
+      </c>
+      <c r="D37">
+        <v>69478</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B38">
+        <v>74.540000000000006</v>
+      </c>
+      <c r="C38">
+        <v>2370</v>
+      </c>
+      <c r="D38">
+        <v>35210</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.66900000000000004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B39">
+        <v>72.86</v>
+      </c>
+      <c r="C39">
+        <v>2320</v>
+      </c>
+      <c r="D39">
+        <v>41021</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B40">
+        <v>75.23</v>
+      </c>
+      <c r="C40">
+        <v>2405</v>
+      </c>
+      <c r="D40">
+        <v>36782</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B41">
+        <v>69.790000000000006</v>
+      </c>
+      <c r="C41">
+        <v>2365</v>
+      </c>
+      <c r="D41">
+        <v>25537</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B42">
+        <v>74.680000000000007</v>
+      </c>
+      <c r="C42">
+        <v>2370</v>
+      </c>
+      <c r="D42">
+        <v>24414</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0.497</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0.497</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B43">
+        <v>75.510000000000005</v>
+      </c>
+      <c r="C43">
+        <v>2380</v>
+      </c>
+      <c r="D43">
+        <v>21498</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.56399999999999995</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B44">
+        <v>78.290000000000006</v>
+      </c>
+      <c r="C44">
+        <v>2395</v>
+      </c>
+      <c r="D44">
+        <v>18248</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.55500000000000005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B45">
+        <v>80.209999999999994</v>
+      </c>
+      <c r="C45">
+        <v>2415</v>
+      </c>
+      <c r="D45">
+        <v>19448</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0.56599999999999995</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B46">
+        <v>79.44</v>
+      </c>
+      <c r="C46">
+        <v>2435</v>
+      </c>
+      <c r="D46">
+        <v>26233</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0.46700000000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B47">
+        <v>77.58</v>
+      </c>
+      <c r="C47">
+        <v>2395</v>
+      </c>
+      <c r="D47">
+        <v>21163</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0.502</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.502</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B48">
+        <v>87.42</v>
+      </c>
+      <c r="C48">
+        <v>2400</v>
+      </c>
+      <c r="D48">
+        <v>13482</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0.70299999999999996</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B49">
+        <v>71.89</v>
+      </c>
+      <c r="C49">
+        <v>2380</v>
+      </c>
+      <c r="D49">
+        <v>19997</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0.48799999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B50">
+        <v>59.68</v>
+      </c>
+      <c r="C50">
+        <v>2350</v>
+      </c>
+      <c r="D50">
+        <v>23619</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0.35199999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B51">
+        <v>62.22</v>
+      </c>
+      <c r="C51">
+        <v>2375</v>
+      </c>
+      <c r="D51">
+        <v>16968</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.38300000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B52">
+        <v>64.92</v>
+      </c>
+      <c r="C52">
+        <v>2410</v>
+      </c>
+      <c r="D52">
+        <v>18922</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.52100000000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B53">
+        <v>56.87</v>
+      </c>
+      <c r="C53">
+        <v>2375</v>
+      </c>
+      <c r="D53">
+        <v>13073</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.30599999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B54">
+        <v>61.54</v>
+      </c>
+      <c r="C54">
+        <v>2400</v>
+      </c>
+      <c r="D54">
+        <v>13538</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0.42199999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B55">
+        <v>72.61</v>
+      </c>
+      <c r="C55">
+        <v>2415</v>
+      </c>
+      <c r="D55">
+        <v>19467</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0.53700000000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B56">
+        <v>81.12</v>
+      </c>
+      <c r="C56">
+        <v>2410</v>
+      </c>
+      <c r="D56">
+        <v>19214</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0.55400000000000005</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B57">
+        <v>85.27</v>
+      </c>
+      <c r="C57">
+        <v>2420</v>
+      </c>
+      <c r="D57">
+        <v>15026</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="F57" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B58">
+        <v>70.94</v>
+      </c>
+      <c r="C58">
+        <v>2405</v>
+      </c>
+      <c r="D58">
+        <v>32793</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.61199999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B59">
+        <v>73.55</v>
+      </c>
+      <c r="C59">
+        <v>2440</v>
+      </c>
+      <c r="D59">
+        <v>31855</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0.53600000000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B60">
+        <v>63.28</v>
+      </c>
+      <c r="C60">
+        <v>2385</v>
+      </c>
+      <c r="D60">
+        <v>25151</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0.41799999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B61">
+        <v>68.02</v>
+      </c>
+      <c r="C61">
+        <v>2390</v>
+      </c>
+      <c r="D61">
+        <v>14252</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0.42599999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B62">
+        <v>72.290000000000006</v>
+      </c>
+      <c r="C62">
+        <v>2410</v>
+      </c>
+      <c r="D62">
+        <v>14102</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0.53300000000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B63">
+        <v>90.35</v>
+      </c>
+      <c r="C63">
+        <v>2460</v>
+      </c>
+      <c r="D63">
+        <v>26898</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.66900000000000004</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B64">
+        <v>84.39</v>
+      </c>
+      <c r="C64">
+        <v>2470</v>
+      </c>
+      <c r="D64">
+        <v>28932</v>
+      </c>
+      <c r="E64" s="3">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0.68899999999999995</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B65">
+        <v>83.36</v>
+      </c>
+      <c r="C65">
+        <v>2465</v>
+      </c>
+      <c r="D65">
+        <v>17799</v>
+      </c>
+      <c r="E65" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="F65" s="4">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B66">
+        <v>72.59</v>
+      </c>
+      <c r="C66">
+        <v>2450</v>
+      </c>
+      <c r="D66">
+        <v>19836</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0.55500000000000005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B67">
+        <v>64.69</v>
+      </c>
+      <c r="C67">
+        <v>2410</v>
+      </c>
+      <c r="D67">
+        <v>21131</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0.53</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B68">
+        <v>57.58</v>
+      </c>
+      <c r="C68">
+        <v>2380</v>
+      </c>
+      <c r="D68">
+        <v>21521</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0.36399999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B69">
+        <v>50.51</v>
+      </c>
+      <c r="C69">
+        <v>2385</v>
+      </c>
+      <c r="D69">
+        <v>15216</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0.21199999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B70">
+        <v>56.63</v>
+      </c>
+      <c r="C70">
+        <v>2380</v>
+      </c>
+      <c r="D70">
+        <v>20919</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0.36499999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B71">
+        <v>70.8</v>
+      </c>
+      <c r="C71">
+        <v>2425</v>
+      </c>
+      <c r="D71">
+        <v>18117</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0.38200000000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B72">
+        <v>82.27</v>
+      </c>
+      <c r="C72">
+        <v>2460</v>
+      </c>
+      <c r="D72">
+        <v>40893</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0.68100000000000005</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59487645-DE44-A846-A962-95AB725026D6}">
+  <dimension ref="A1:F72"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="15.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B2">
+        <v>51.16</v>
+      </c>
+      <c r="C2">
+        <v>263</v>
+      </c>
+      <c r="D2">
+        <v>93369</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B3">
+        <v>61.28</v>
+      </c>
+      <c r="C3">
+        <v>258.5</v>
+      </c>
+      <c r="D3">
+        <v>97551</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B4">
+        <v>65.489999999999995</v>
+      </c>
+      <c r="C4">
+        <v>260.5</v>
+      </c>
+      <c r="D4">
+        <v>60261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B5">
+        <v>86.29</v>
+      </c>
+      <c r="C5">
+        <v>267.5</v>
+      </c>
+      <c r="D5">
+        <v>54689</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B6">
+        <v>86.43</v>
+      </c>
+      <c r="C6">
+        <v>269</v>
+      </c>
+      <c r="D6">
+        <v>56879</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B7">
+        <v>73.47</v>
+      </c>
+      <c r="C7">
+        <v>272</v>
+      </c>
+      <c r="D7">
+        <v>42755</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B8">
+        <v>78.55</v>
+      </c>
+      <c r="C8">
+        <v>268.5</v>
+      </c>
+      <c r="D8">
+        <v>68997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B9">
+        <v>94.59</v>
+      </c>
+      <c r="C9">
+        <v>268.5</v>
+      </c>
+      <c r="D9">
+        <v>67146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B10">
+        <v>78.2</v>
+      </c>
+      <c r="C10">
+        <v>259.5</v>
+      </c>
+      <c r="D10">
+        <v>92064</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B11">
+        <v>67.39</v>
+      </c>
+      <c r="C11">
+        <v>256</v>
+      </c>
+      <c r="D11">
+        <v>63691</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B12">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="C12">
+        <v>257.5</v>
+      </c>
+      <c r="D12">
+        <v>43578</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B13">
+        <v>58.05</v>
+      </c>
+      <c r="C13">
+        <v>248.5</v>
+      </c>
+      <c r="D13">
+        <v>80451</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B14">
+        <v>68.03</v>
+      </c>
+      <c r="C14">
+        <v>246.5</v>
+      </c>
+      <c r="D14">
+        <v>49210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B15">
+        <v>79.33</v>
+      </c>
+      <c r="C15">
+        <v>251</v>
+      </c>
+      <c r="D15">
+        <v>52952</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B16">
+        <v>85.52</v>
+      </c>
+      <c r="C16">
+        <v>248</v>
+      </c>
+      <c r="D16">
+        <v>65881</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B17">
+        <v>74.48</v>
+      </c>
+      <c r="C17">
+        <v>239</v>
+      </c>
+      <c r="D17">
+        <v>67897</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B18">
+        <v>68.53</v>
+      </c>
+      <c r="C18">
+        <v>240.5</v>
+      </c>
+      <c r="D18">
+        <v>51008</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B19">
+        <v>78.239999999999995</v>
+      </c>
+      <c r="C19">
+        <v>242</v>
+      </c>
+      <c r="D19">
+        <v>43694</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B20">
+        <v>71.17</v>
+      </c>
+      <c r="C20">
+        <v>237</v>
+      </c>
+      <c r="D20">
+        <v>51779</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B21">
+        <v>64.37</v>
+      </c>
+      <c r="C21">
+        <v>237.5</v>
+      </c>
+      <c r="D21">
+        <v>37939</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B22">
+        <v>58.23</v>
+      </c>
+      <c r="C22">
+        <v>237.5</v>
+      </c>
+      <c r="D22">
+        <v>40528</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B23">
+        <v>63.35</v>
+      </c>
+      <c r="C23">
+        <v>236.5</v>
+      </c>
+      <c r="D23">
+        <v>37505</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B24">
+        <v>58.64</v>
+      </c>
+      <c r="C24">
+        <v>235.5</v>
+      </c>
+      <c r="D24">
+        <v>48112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B25">
+        <v>68.349999999999994</v>
+      </c>
+      <c r="C25">
+        <v>239</v>
+      </c>
+      <c r="D25">
+        <v>36109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B26">
+        <v>57.84</v>
+      </c>
+      <c r="C26">
+        <v>242.5</v>
+      </c>
+      <c r="D26">
+        <v>39075</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B27">
+        <v>57.5</v>
+      </c>
+      <c r="C27">
+        <v>234</v>
+      </c>
+      <c r="D27">
+        <v>69007</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B28">
+        <v>61.53</v>
+      </c>
+      <c r="C28">
+        <v>234.5</v>
+      </c>
+      <c r="D28">
+        <v>48580</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B29">
+        <v>75.09</v>
+      </c>
+      <c r="C29">
+        <v>246</v>
+      </c>
+      <c r="D29">
+        <v>51471</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B30">
+        <v>82.22</v>
+      </c>
+      <c r="C30">
+        <v>251.5</v>
+      </c>
+      <c r="D30">
+        <v>67787</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B31">
+        <v>89.1</v>
+      </c>
+      <c r="C31">
+        <v>257.5</v>
+      </c>
+      <c r="D31">
+        <v>63788</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B32">
+        <v>90</v>
+      </c>
+      <c r="C32">
+        <v>252.5</v>
+      </c>
+      <c r="D32">
+        <v>33695</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B33">
+        <v>90</v>
+      </c>
+      <c r="C33">
+        <v>253</v>
+      </c>
+      <c r="D33">
+        <v>35908</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B34">
+        <v>27.32</v>
+      </c>
+      <c r="C34">
+        <v>238</v>
+      </c>
+      <c r="D34">
+        <v>52860</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B35">
+        <v>30.83</v>
+      </c>
+      <c r="C35">
+        <v>237</v>
+      </c>
+      <c r="D35">
+        <v>84937</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B36">
+        <v>39.25</v>
+      </c>
+      <c r="C36">
+        <v>229.5</v>
+      </c>
+      <c r="D36">
+        <v>77133</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0.66400000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B37">
+        <v>64.95</v>
+      </c>
+      <c r="C37">
+        <v>250.5</v>
+      </c>
+      <c r="D37">
+        <v>99414</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0.47299999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B38">
+        <v>84.32</v>
+      </c>
+      <c r="C38">
+        <v>253</v>
+      </c>
+      <c r="D38">
+        <v>52666</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.41699999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B39">
+        <v>72.41</v>
+      </c>
+      <c r="C39">
+        <v>250</v>
+      </c>
+      <c r="D39">
+        <v>41096</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0.41799999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B40">
+        <v>79.69</v>
+      </c>
+      <c r="C40">
+        <v>258.5</v>
+      </c>
+      <c r="D40">
+        <v>72634</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0.59499999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B41">
+        <v>68.3</v>
+      </c>
+      <c r="C41">
+        <v>264.5</v>
+      </c>
+      <c r="D41">
+        <v>82179</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.374</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.374</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B42">
+        <v>75.19</v>
+      </c>
+      <c r="C42">
+        <v>260</v>
+      </c>
+      <c r="D42">
+        <v>38813</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0.41099999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B43">
+        <v>88.66</v>
+      </c>
+      <c r="C43">
+        <v>264.5</v>
+      </c>
+      <c r="D43">
+        <v>34854</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B44">
+        <v>85.26</v>
+      </c>
+      <c r="C44">
+        <v>263</v>
+      </c>
+      <c r="D44">
+        <v>24592</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.251</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.30199999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B45">
+        <v>83.07</v>
+      </c>
+      <c r="C45">
+        <v>270</v>
+      </c>
+      <c r="D45">
+        <v>60316</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0.309</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0.309</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B46">
+        <v>83.9</v>
+      </c>
+      <c r="C46">
+        <v>262</v>
+      </c>
+      <c r="D46">
+        <v>96830</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0.60699999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B47">
+        <v>81.38</v>
+      </c>
+      <c r="C47">
+        <v>259.5</v>
+      </c>
+      <c r="D47">
+        <v>51014</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0.753</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.753</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B48">
+        <v>85.12</v>
+      </c>
+      <c r="C48">
+        <v>255</v>
+      </c>
+      <c r="D48">
+        <v>35552</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0.439</v>
+      </c>
+      <c r="F48" s="4">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B49">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="C49">
+        <v>249</v>
+      </c>
+      <c r="D49">
+        <v>50540</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0.29899999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B50">
+        <v>69.64</v>
+      </c>
+      <c r="C50">
+        <v>245</v>
+      </c>
+      <c r="D50">
+        <v>36593</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0.68400000000000005</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B51">
+        <v>69.28</v>
+      </c>
+      <c r="C51">
+        <v>246.5</v>
+      </c>
+      <c r="D51">
+        <v>26344</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.40500000000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B52">
+        <v>71.27</v>
+      </c>
+      <c r="C52">
+        <v>245.5</v>
+      </c>
+      <c r="D52">
+        <v>25420</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.59099999999999997</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B53">
+        <v>76.77</v>
+      </c>
+      <c r="C53">
+        <v>243.5</v>
+      </c>
+      <c r="D53">
+        <v>23691</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.65600000000000003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B54">
+        <v>72.58</v>
+      </c>
+      <c r="C54">
+        <v>243</v>
+      </c>
+      <c r="D54">
+        <v>36819</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0.32900000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B55">
+        <v>74.75</v>
+      </c>
+      <c r="C55">
+        <v>246.5</v>
+      </c>
+      <c r="D55">
+        <v>24910</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B56">
+        <v>79.66</v>
+      </c>
+      <c r="C56">
+        <v>252</v>
+      </c>
+      <c r="D56">
+        <v>42280</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0.38300000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B57">
+        <v>83.53</v>
+      </c>
+      <c r="C57">
+        <v>253</v>
+      </c>
+      <c r="D57">
+        <v>31847</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0.42199999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B58">
+        <v>74.08</v>
+      </c>
+      <c r="C58">
+        <v>250</v>
+      </c>
+      <c r="D58">
+        <v>35223</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.38700000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B59">
+        <v>73.95</v>
+      </c>
+      <c r="C59">
+        <v>256</v>
+      </c>
+      <c r="D59">
+        <v>34132</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0.40100000000000002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B60">
+        <v>67.239999999999995</v>
+      </c>
+      <c r="C60">
+        <v>251</v>
+      </c>
+      <c r="D60">
+        <v>29265</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0.32800000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B61">
+        <v>73.510000000000005</v>
+      </c>
+      <c r="C61">
+        <v>247.5</v>
+      </c>
+      <c r="D61">
+        <v>29851</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0.45500000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B62">
+        <v>74.45</v>
+      </c>
+      <c r="C62">
+        <v>256</v>
+      </c>
+      <c r="D62">
+        <v>49402</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0.39400000000000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B63">
+        <v>84.16</v>
+      </c>
+      <c r="C63">
+        <v>256</v>
+      </c>
+      <c r="D63">
+        <v>34027</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.41399999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B64">
+        <v>83.36</v>
+      </c>
+      <c r="C64">
+        <v>251.5</v>
+      </c>
+      <c r="D64">
+        <v>40241</v>
+      </c>
+      <c r="E64" s="3">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0.38400000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B65">
+        <v>79.849999999999994</v>
+      </c>
+      <c r="C65">
+        <v>252</v>
+      </c>
+      <c r="D65">
+        <v>21344</v>
+      </c>
+      <c r="E65" s="3">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0.36899999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B66">
+        <v>71.150000000000006</v>
+      </c>
+      <c r="C66">
+        <v>251</v>
+      </c>
+      <c r="D66">
+        <v>40234</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0.48699999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B67">
+        <v>64.58</v>
+      </c>
+      <c r="C67">
+        <v>248</v>
+      </c>
+      <c r="D67">
+        <v>24164</v>
+      </c>
+      <c r="E67" s="3">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0.57099999999999995</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B68">
+        <v>55.87</v>
+      </c>
+      <c r="C68">
+        <v>248.5</v>
+      </c>
+      <c r="D68">
+        <v>25261</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0.503</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0.503</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B69">
+        <v>45.84</v>
+      </c>
+      <c r="C69">
+        <v>246.5</v>
+      </c>
+      <c r="D69">
+        <v>15812</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0.27300000000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B70">
+        <v>51.81</v>
+      </c>
+      <c r="C70">
+        <v>248</v>
+      </c>
+      <c r="D70">
+        <v>19737</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0.438</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B71">
+        <v>67.63</v>
+      </c>
+      <c r="C71">
+        <v>250.5</v>
+      </c>
+      <c r="D71">
+        <v>26522</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0.378</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0.378</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B72">
+        <v>82.02</v>
+      </c>
+      <c r="C72">
+        <v>250.5</v>
+      </c>
+      <c r="D72">
+        <v>44803</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0.38600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5443,233 +11077,243 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59487645-DE44-A846-A962-95AB725026D6}">
-  <dimension ref="A1:E35"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94EA143E-4671-5B40-B9E6-8E3DD8AC65E4}">
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="15.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46183</v>
       </c>
       <c r="B2">
-        <v>51.16</v>
+        <v>63.21</v>
       </c>
       <c r="C2">
-        <v>263</v>
+        <v>4155</v>
       </c>
       <c r="D2">
-        <v>93369</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17413</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46184</v>
       </c>
       <c r="B3">
-        <v>61.28</v>
+        <v>67.72</v>
       </c>
       <c r="C3">
-        <v>258.5</v>
+        <v>4085</v>
       </c>
       <c r="D3">
-        <v>97551</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17557</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46185</v>
       </c>
       <c r="B4">
-        <v>65.489999999999995</v>
+        <v>66.3</v>
       </c>
       <c r="C4">
-        <v>260.5</v>
+        <v>4180</v>
       </c>
       <c r="D4">
-        <v>60261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8765</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46188</v>
       </c>
       <c r="B5">
-        <v>86.29</v>
+        <v>88.06</v>
       </c>
       <c r="C5">
-        <v>267.5</v>
+        <v>4470</v>
       </c>
       <c r="D5">
-        <v>54689</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12015</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46189</v>
       </c>
       <c r="B6">
-        <v>86.43</v>
+        <v>88.29</v>
       </c>
       <c r="C6">
-        <v>269</v>
+        <v>4560</v>
       </c>
       <c r="D6">
-        <v>56879</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46190</v>
       </c>
       <c r="B7">
-        <v>73.47</v>
+        <v>80.58</v>
       </c>
       <c r="C7">
-        <v>272</v>
+        <v>4460</v>
       </c>
       <c r="D7">
-        <v>42755</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46191</v>
       </c>
       <c r="B8">
-        <v>78.55</v>
+        <v>80.13</v>
       </c>
       <c r="C8">
-        <v>268.5</v>
+        <v>4390</v>
       </c>
       <c r="D8">
-        <v>68997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46195</v>
       </c>
       <c r="B9">
-        <v>94.59</v>
+        <v>94.19</v>
       </c>
       <c r="C9">
-        <v>268.5</v>
+        <v>4465</v>
       </c>
       <c r="D9">
-        <v>67146</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11596</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46196</v>
       </c>
       <c r="B10">
-        <v>78.2</v>
+        <v>79.87</v>
       </c>
       <c r="C10">
-        <v>259.5</v>
+        <v>4535</v>
       </c>
       <c r="D10">
-        <v>92064</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46197</v>
       </c>
       <c r="B11">
-        <v>67.39</v>
+        <v>68.64</v>
       </c>
       <c r="C11">
-        <v>256</v>
+        <v>4285</v>
       </c>
       <c r="D11">
-        <v>63691</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16421</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46198</v>
       </c>
       <c r="B12">
-        <v>64.099999999999994</v>
+        <v>66.31</v>
       </c>
       <c r="C12">
-        <v>257.5</v>
+        <v>4310</v>
       </c>
       <c r="D12">
-        <v>43578</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46199</v>
       </c>
       <c r="B13">
-        <v>58.05</v>
+        <v>61.87</v>
       </c>
       <c r="C13">
-        <v>248.5</v>
+        <v>3880</v>
       </c>
       <c r="D13">
-        <v>80451</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>24916</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46202</v>
       </c>
       <c r="B14">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="C14">
-        <v>246.5</v>
+        <v>3910</v>
       </c>
       <c r="D14">
-        <v>49210</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11358</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46203</v>
       </c>
       <c r="B15">
-        <v>79.33</v>
+        <v>79.95</v>
       </c>
       <c r="C15">
-        <v>251</v>
+        <v>4245</v>
       </c>
       <c r="D15">
-        <v>52952</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16095</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46204</v>
       </c>
       <c r="B16">
-        <v>85.52</v>
+        <v>85.94</v>
       </c>
       <c r="C16">
-        <v>248</v>
+        <v>4335</v>
       </c>
       <c r="D16">
-        <v>65881</v>
+        <v>10164</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5677,13 +11321,13 @@
         <v>46205</v>
       </c>
       <c r="B17">
-        <v>74.48</v>
+        <v>83.45</v>
       </c>
       <c r="C17">
-        <v>239</v>
+        <v>4345</v>
       </c>
       <c r="D17">
-        <v>67897</v>
+        <v>8544</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5691,13 +11335,13 @@
         <v>46206</v>
       </c>
       <c r="B18">
-        <v>68.53</v>
+        <v>73.510000000000005</v>
       </c>
       <c r="C18">
-        <v>240.5</v>
+        <v>4195</v>
       </c>
       <c r="D18">
-        <v>51008</v>
+        <v>12778</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5705,13 +11349,13 @@
         <v>46209</v>
       </c>
       <c r="B19">
-        <v>78.239999999999995</v>
+        <v>72.959999999999994</v>
       </c>
       <c r="C19">
-        <v>242</v>
+        <v>4125</v>
       </c>
       <c r="D19">
-        <v>43694</v>
+        <v>6897</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5719,13 +11363,13 @@
         <v>46210</v>
       </c>
       <c r="B20">
-        <v>71.17</v>
+        <v>67.89</v>
       </c>
       <c r="C20">
-        <v>237</v>
+        <v>4030</v>
       </c>
       <c r="D20">
-        <v>51779</v>
+        <v>9083</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5733,13 +11377,13 @@
         <v>46211</v>
       </c>
       <c r="B21">
-        <v>64.37</v>
+        <v>66.45</v>
       </c>
       <c r="C21">
-        <v>237.5</v>
+        <v>3995</v>
       </c>
       <c r="D21">
-        <v>37939</v>
+        <v>6728</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5747,13 +11391,13 @@
         <v>46212</v>
       </c>
       <c r="B22">
-        <v>58.23</v>
+        <v>60.64</v>
       </c>
       <c r="C22">
-        <v>237.5</v>
+        <v>3925</v>
       </c>
       <c r="D22">
-        <v>40528</v>
+        <v>7371</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5761,13 +11405,13 @@
         <v>46216</v>
       </c>
       <c r="B23">
-        <v>63.35</v>
+        <v>66.73</v>
       </c>
       <c r="C23">
-        <v>236.5</v>
+        <v>3825</v>
       </c>
       <c r="D23">
-        <v>37505</v>
+        <v>7033</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5775,13 +11419,13 @@
         <v>46217</v>
       </c>
       <c r="B24">
-        <v>58.64</v>
+        <v>61.86</v>
       </c>
       <c r="C24">
-        <v>235.5</v>
+        <v>3660</v>
       </c>
       <c r="D24">
-        <v>48112</v>
+        <v>12480</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5789,13 +11433,13 @@
         <v>46218</v>
       </c>
       <c r="B25">
-        <v>68.349999999999994</v>
+        <v>71.97</v>
       </c>
       <c r="C25">
-        <v>239</v>
+        <v>3740</v>
       </c>
       <c r="D25">
-        <v>36109</v>
+        <v>7314</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5803,13 +11447,13 @@
         <v>46219</v>
       </c>
       <c r="B26">
-        <v>57.84</v>
+        <v>60.53</v>
       </c>
       <c r="C26">
-        <v>242.5</v>
+        <v>3700</v>
       </c>
       <c r="D26">
-        <v>39075</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5817,13 +11461,13 @@
         <v>46220</v>
       </c>
       <c r="B27">
-        <v>57.5</v>
+        <v>58.52</v>
       </c>
       <c r="C27">
-        <v>234</v>
+        <v>3370</v>
       </c>
       <c r="D27">
-        <v>69007</v>
+        <v>10967</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5831,13 +11475,13 @@
         <v>46223</v>
       </c>
       <c r="B28">
-        <v>61.53</v>
+        <v>58.77</v>
       </c>
       <c r="C28">
-        <v>234.5</v>
+        <v>3340</v>
       </c>
       <c r="D28">
-        <v>48580</v>
+        <v>9228</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5845,13 +11489,13 @@
         <v>46224</v>
       </c>
       <c r="B29">
-        <v>75.09</v>
+        <v>73.459999999999994</v>
       </c>
       <c r="C29">
-        <v>246</v>
+        <v>3670</v>
       </c>
       <c r="D29">
-        <v>51471</v>
+        <v>7742</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5859,13 +11503,13 @@
         <v>46225</v>
       </c>
       <c r="B30">
-        <v>82.22</v>
+        <v>78.55</v>
       </c>
       <c r="C30">
-        <v>251.5</v>
+        <v>3850</v>
       </c>
       <c r="D30">
-        <v>67787</v>
+        <v>13767</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5873,13 +11517,13 @@
         <v>46226</v>
       </c>
       <c r="B31">
-        <v>89.1</v>
+        <v>85.25</v>
       </c>
       <c r="C31">
-        <v>257.5</v>
+        <v>3875</v>
       </c>
       <c r="D31">
-        <v>63788</v>
+        <v>8514</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5887,581 +11531,1639 @@
         <v>46227</v>
       </c>
       <c r="B32">
-        <v>90</v>
+        <v>66.33</v>
       </c>
       <c r="C32">
-        <v>252.5</v>
+        <v>3750</v>
       </c>
       <c r="D32">
-        <v>33695</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8980</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46230</v>
       </c>
       <c r="B33">
-        <v>90</v>
+        <v>66.33</v>
       </c>
       <c r="C33">
-        <v>253</v>
+        <v>3680</v>
       </c>
       <c r="D33">
-        <v>35908</v>
+        <v>9134</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46231</v>
       </c>
       <c r="B34">
-        <v>27.32</v>
+        <v>20.83</v>
       </c>
       <c r="C34">
-        <v>238</v>
+        <v>3315</v>
       </c>
       <c r="D34">
-        <v>52860</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11959</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46232</v>
       </c>
       <c r="B35">
-        <v>30.83</v>
+        <v>21.76</v>
       </c>
       <c r="C35">
-        <v>237</v>
+        <v>3150</v>
       </c>
       <c r="D35">
-        <v>84937</v>
+        <v>16174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B36">
+        <v>31.72</v>
+      </c>
+      <c r="C36">
+        <v>3235</v>
+      </c>
+      <c r="D36">
+        <v>14126</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0.46400000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B37">
+        <v>61.6</v>
+      </c>
+      <c r="C37">
+        <v>3555</v>
+      </c>
+      <c r="D37">
+        <v>4033</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0.75700000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B38">
+        <v>77.38</v>
+      </c>
+      <c r="C38">
+        <v>3910</v>
+      </c>
+      <c r="D38">
+        <v>7516</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.44600000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B39">
+        <v>72.63</v>
+      </c>
+      <c r="C39">
+        <v>3865</v>
+      </c>
+      <c r="D39">
+        <v>17319</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0.79100000000000004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B40">
+        <v>75.739999999999995</v>
+      </c>
+      <c r="C40">
+        <v>4000</v>
+      </c>
+      <c r="D40">
+        <v>12935</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0.33700000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B41">
+        <v>65.989999999999995</v>
+      </c>
+      <c r="C41">
+        <v>3920</v>
+      </c>
+      <c r="D41">
+        <v>7213</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.54100000000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B42">
+        <v>69.42</v>
+      </c>
+      <c r="C42">
+        <v>3900</v>
+      </c>
+      <c r="D42">
+        <v>6607</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0.57199999999999995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B43">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="C43">
+        <v>3960</v>
+      </c>
+      <c r="D43">
+        <v>5873</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.55300000000000005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B44">
+        <v>77.42</v>
+      </c>
+      <c r="C44">
+        <v>4020</v>
+      </c>
+      <c r="D44">
+        <v>7709</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.43099999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B45">
+        <v>78.56</v>
+      </c>
+      <c r="C45">
+        <v>4015</v>
+      </c>
+      <c r="D45">
+        <v>6018</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0.49299999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B46">
+        <v>79.48</v>
+      </c>
+      <c r="C46">
+        <v>4225</v>
+      </c>
+      <c r="D46">
+        <v>12264</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0.56699999999999995</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B47">
+        <v>77.680000000000007</v>
+      </c>
+      <c r="C47">
+        <v>4210</v>
+      </c>
+      <c r="D47">
+        <v>10696</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.55700000000000005</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B48">
+        <v>77.8</v>
+      </c>
+      <c r="C48">
+        <v>4050</v>
+      </c>
+      <c r="D48">
+        <v>10560</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0.65800000000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B49">
+        <v>71.010000000000005</v>
+      </c>
+      <c r="C49">
+        <v>3885</v>
+      </c>
+      <c r="D49">
+        <v>9324</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0.61499999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B50">
+        <v>57.71</v>
+      </c>
+      <c r="C50">
+        <v>3845</v>
+      </c>
+      <c r="D50">
+        <v>7037</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0.46300000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B51">
+        <v>58.78</v>
+      </c>
+      <c r="C51">
+        <v>3700</v>
+      </c>
+      <c r="D51">
+        <v>13214</v>
+      </c>
+      <c r="E51" s="4">
+        <v>0.44</v>
+      </c>
+      <c r="F51" s="4">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B52">
+        <v>60.1</v>
+      </c>
+      <c r="C52">
+        <v>3790</v>
+      </c>
+      <c r="D52">
+        <v>6657</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B53">
+        <v>64.06</v>
+      </c>
+      <c r="C53">
+        <v>3765</v>
+      </c>
+      <c r="D53">
+        <v>3321</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.73299999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B54">
+        <v>63.79</v>
+      </c>
+      <c r="C54">
+        <v>3735</v>
+      </c>
+      <c r="D54">
+        <v>5403</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0.311</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B55">
+        <v>71.23</v>
+      </c>
+      <c r="C55">
+        <v>3945</v>
+      </c>
+      <c r="D55">
+        <v>8370</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0.48199999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B56">
+        <v>77.8</v>
+      </c>
+      <c r="C56">
+        <v>3865</v>
+      </c>
+      <c r="D56">
+        <v>5703</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0.46200000000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B57">
+        <v>81.44</v>
+      </c>
+      <c r="C57">
+        <v>3985</v>
+      </c>
+      <c r="D57">
+        <v>5065</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0.434</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0.434</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B58">
+        <v>56.8</v>
+      </c>
+      <c r="C58">
+        <v>3925</v>
+      </c>
+      <c r="D58">
+        <v>7222</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.46400000000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B59">
+        <v>69.680000000000007</v>
+      </c>
+      <c r="C59">
+        <v>4315</v>
+      </c>
+      <c r="D59">
+        <v>4932</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0.501</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0.501</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B60">
+        <v>57.4</v>
+      </c>
+      <c r="C60">
+        <v>4275</v>
+      </c>
+      <c r="D60">
+        <v>23567</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0.60699999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B61">
+        <v>63.02</v>
+      </c>
+      <c r="C61">
+        <v>4340</v>
+      </c>
+      <c r="D61">
+        <v>9510</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0.29899999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B62">
+        <v>66.760000000000005</v>
+      </c>
+      <c r="C62">
+        <v>4415</v>
+      </c>
+      <c r="D62">
+        <v>9052</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0.48699999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B63">
+        <v>89.68</v>
+      </c>
+      <c r="C63">
+        <v>4760</v>
+      </c>
+      <c r="D63">
+        <v>17178</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.66400000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B64">
+        <v>84.58</v>
+      </c>
+      <c r="C64">
+        <v>4710</v>
+      </c>
+      <c r="D64">
+        <v>6512</v>
+      </c>
+      <c r="E64" s="3">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0.50900000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B65">
+        <v>82.97</v>
+      </c>
+      <c r="C65">
+        <v>4625</v>
+      </c>
+      <c r="D65">
+        <v>5401</v>
+      </c>
+      <c r="E65" s="3">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0.41799999999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B66">
+        <v>70.010000000000005</v>
+      </c>
+      <c r="C66">
+        <v>4720</v>
+      </c>
+      <c r="D66">
+        <v>6662</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0.23499999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B67">
+        <v>56.84</v>
+      </c>
+      <c r="C67">
+        <v>4585</v>
+      </c>
+      <c r="D67">
+        <v>7592</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B68">
+        <v>55</v>
+      </c>
+      <c r="C68">
+        <v>4560</v>
+      </c>
+      <c r="D68">
+        <v>6123</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0.503</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0.503</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B69">
+        <v>50.13</v>
+      </c>
+      <c r="C69">
+        <v>4430</v>
+      </c>
+      <c r="D69">
+        <v>6209</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0.50700000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B70">
+        <v>60.9</v>
+      </c>
+      <c r="C70">
+        <v>4530</v>
+      </c>
+      <c r="D70">
+        <v>6641</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0.54300000000000004</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B71">
+        <v>70.75</v>
+      </c>
+      <c r="C71">
+        <v>4500</v>
+      </c>
+      <c r="D71">
+        <v>6496</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0.33800000000000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B72">
+        <v>84.55</v>
+      </c>
+      <c r="C72">
+        <v>4710</v>
+      </c>
+      <c r="D72">
+        <v>10365</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0.50700000000000001</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94EA143E-4671-5B40-B9E6-8E3DD8AC65E4}">
-  <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F8EB60-3A79-4995-BB12-AF7188F54CF4}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46183</v>
+        <v>46218</v>
       </c>
       <c r="B2">
-        <v>63.21</v>
+        <v>74.81</v>
       </c>
       <c r="C2">
-        <v>4155</v>
+        <v>481</v>
       </c>
       <c r="D2">
-        <v>17413</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>158461</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46184</v>
+        <v>46219</v>
       </c>
       <c r="B3">
-        <v>67.72</v>
+        <v>75.28</v>
       </c>
       <c r="C3">
-        <v>4085</v>
+        <v>439</v>
       </c>
       <c r="D3">
-        <v>17557</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46185</v>
+        <v>46220</v>
       </c>
       <c r="B4">
-        <v>66.3</v>
+        <v>71.040000000000006</v>
       </c>
       <c r="C4">
-        <v>4180</v>
+        <v>395.5</v>
       </c>
       <c r="D4">
-        <v>8765</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>82626</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46188</v>
+        <v>46223</v>
       </c>
       <c r="B5">
-        <v>88.06</v>
+        <v>67.92</v>
       </c>
       <c r="C5">
-        <v>4470</v>
+        <v>381</v>
       </c>
       <c r="D5">
-        <v>12015</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73602</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46189</v>
+        <v>46224</v>
       </c>
       <c r="B6">
-        <v>88.29</v>
+        <v>75.27</v>
       </c>
       <c r="C6">
-        <v>4560</v>
+        <v>405</v>
       </c>
       <c r="D6">
-        <v>11310</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70571</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="B7">
-        <v>80.58</v>
+        <v>77.89</v>
       </c>
       <c r="C7">
-        <v>4460</v>
+        <v>445.5</v>
       </c>
       <c r="D7">
-        <v>9198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63907</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46191</v>
+        <v>46226</v>
       </c>
       <c r="B8">
-        <v>80.13</v>
+        <v>77.86</v>
       </c>
       <c r="C8">
-        <v>4390</v>
+        <v>426</v>
       </c>
       <c r="D8">
-        <v>12998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>89387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46195</v>
+        <v>46227</v>
       </c>
       <c r="B9">
-        <v>94.19</v>
+        <v>72.47</v>
       </c>
       <c r="C9">
-        <v>4465</v>
+        <v>401</v>
       </c>
       <c r="D9">
-        <v>11596</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>80046</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46196</v>
+        <v>46230</v>
       </c>
       <c r="B10">
-        <v>79.87</v>
+        <v>69.3</v>
       </c>
       <c r="C10">
-        <v>4535</v>
+        <v>436</v>
       </c>
       <c r="D10">
-        <v>18450</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>81191</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46197</v>
+        <v>46231</v>
       </c>
       <c r="B11">
-        <v>68.64</v>
+        <v>51.82</v>
       </c>
       <c r="C11">
-        <v>4285</v>
+        <v>392.5</v>
       </c>
       <c r="D11">
-        <v>16421</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>60941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>46198</v>
+        <v>46232</v>
       </c>
       <c r="B12">
-        <v>66.31</v>
+        <v>49.97</v>
       </c>
       <c r="C12">
-        <v>4310</v>
+        <v>353.5</v>
       </c>
       <c r="D12">
-        <v>10274</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56513</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>46199</v>
+        <v>46233</v>
       </c>
       <c r="B13">
-        <v>61.87</v>
+        <v>48.44</v>
       </c>
       <c r="C13">
-        <v>3880</v>
+        <v>328</v>
       </c>
       <c r="D13">
-        <v>24916</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>120154</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.53200000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>46202</v>
+        <v>46234</v>
       </c>
       <c r="B14">
-        <v>69.47</v>
+        <v>61.29</v>
       </c>
       <c r="C14">
-        <v>3910</v>
+        <v>360.5</v>
       </c>
       <c r="D14">
-        <v>11358</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8135</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.45400000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>46203</v>
+        <v>46237</v>
       </c>
       <c r="B15">
-        <v>79.95</v>
+        <v>74.98</v>
       </c>
       <c r="C15">
-        <v>4245</v>
+        <v>396.5</v>
       </c>
       <c r="D15">
-        <v>16095</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="B16">
-        <v>85.94</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="C16">
-        <v>4335</v>
+        <v>436</v>
       </c>
       <c r="D16">
-        <v>10164</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119677</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>46205</v>
+        <v>46239</v>
       </c>
       <c r="B17">
-        <v>83.45</v>
+        <v>77.83</v>
       </c>
       <c r="C17">
-        <v>4345</v>
+        <v>445</v>
       </c>
       <c r="D17">
-        <v>8544</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>144426</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.40400000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>46206</v>
+        <v>46240</v>
       </c>
       <c r="B18">
-        <v>73.510000000000005</v>
+        <v>75.349999999999994</v>
       </c>
       <c r="C18">
-        <v>4195</v>
+        <v>459</v>
       </c>
       <c r="D18">
-        <v>12778</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>106681</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>46209</v>
+        <v>46241</v>
       </c>
       <c r="B19">
-        <v>72.959999999999994</v>
+        <v>75.28</v>
       </c>
       <c r="C19">
-        <v>4125</v>
+        <v>457</v>
       </c>
       <c r="D19">
-        <v>6897</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70548</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.35200000000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>46210</v>
+        <v>46244</v>
       </c>
       <c r="B20">
-        <v>67.89</v>
+        <v>91.62</v>
       </c>
       <c r="C20">
-        <v>4030</v>
+        <v>502</v>
       </c>
       <c r="D20">
-        <v>9083</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102645</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>46211</v>
+        <v>46245</v>
       </c>
       <c r="B21">
-        <v>66.45</v>
+        <v>87.25</v>
       </c>
       <c r="C21">
-        <v>3995</v>
+        <v>489</v>
       </c>
       <c r="D21">
-        <v>6728</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>114282</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>46212</v>
+        <v>46246</v>
       </c>
       <c r="B22">
-        <v>60.64</v>
+        <v>84.46</v>
       </c>
       <c r="C22">
-        <v>3925</v>
+        <v>482.5</v>
       </c>
       <c r="D22">
-        <v>7371</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>93649</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>46216</v>
+        <v>46247</v>
       </c>
       <c r="B23">
-        <v>66.73</v>
+        <v>81.66</v>
       </c>
       <c r="C23">
-        <v>3825</v>
+        <v>514</v>
       </c>
       <c r="D23">
-        <v>7033</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>128575</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.371</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>46217</v>
+        <v>46248</v>
       </c>
       <c r="B24">
-        <v>61.86</v>
+        <v>79.27</v>
       </c>
       <c r="C24">
-        <v>3660</v>
+        <v>512</v>
       </c>
       <c r="D24">
-        <v>12480</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>104565</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.42699999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>46218</v>
+        <v>46251</v>
       </c>
       <c r="B25">
-        <v>71.97</v>
+        <v>80.150000000000006</v>
       </c>
       <c r="C25">
-        <v>3740</v>
+        <v>524</v>
       </c>
       <c r="D25">
-        <v>7314</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62244</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.44800000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>46219</v>
+        <v>46252</v>
       </c>
       <c r="B26">
-        <v>60.53</v>
+        <v>66.069999999999993</v>
       </c>
       <c r="C26">
-        <v>3700</v>
+        <v>515</v>
       </c>
       <c r="D26">
-        <v>6010</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85566</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.57599999999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>46220</v>
+        <v>46253</v>
       </c>
       <c r="B27">
-        <v>58.52</v>
+        <v>55.18</v>
       </c>
       <c r="C27">
-        <v>3370</v>
+        <v>481</v>
       </c>
       <c r="D27">
-        <v>10967</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69158</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="B28">
-        <v>58.77</v>
+        <v>60.55</v>
       </c>
       <c r="C28">
-        <v>3340</v>
+        <v>517</v>
       </c>
       <c r="D28">
-        <v>9228</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>88103</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0.61099999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="B29">
-        <v>73.459999999999994</v>
+        <v>70.23</v>
       </c>
       <c r="C29">
-        <v>3670</v>
+        <v>528</v>
       </c>
       <c r="D29">
-        <v>7742</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65354</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.623</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>46225</v>
+        <v>46258</v>
       </c>
       <c r="B30">
-        <v>78.55</v>
+        <v>72.64</v>
       </c>
       <c r="C30">
-        <v>3850</v>
+        <v>501</v>
       </c>
       <c r="D30">
-        <v>13767</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71724</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0.47799999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>46226</v>
+        <v>46259</v>
       </c>
       <c r="B31">
-        <v>85.25</v>
+        <v>67.88</v>
       </c>
       <c r="C31">
-        <v>3875</v>
+        <v>510</v>
       </c>
       <c r="D31">
-        <v>8514</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66841</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.36199999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>46227</v>
+        <v>46260</v>
       </c>
       <c r="B32">
-        <v>66.33</v>
+        <v>71.08</v>
       </c>
       <c r="C32">
-        <v>3750</v>
+        <v>517</v>
       </c>
       <c r="D32">
-        <v>8980</v>
+        <v>61614</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.29399999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="B33">
-        <v>66.33</v>
+        <v>79.17</v>
       </c>
       <c r="C33">
-        <v>3680</v>
+        <v>541</v>
       </c>
       <c r="D33">
-        <v>9134</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
+        <v>87536</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.72299999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="B34">
-        <v>20.83</v>
+        <v>83.32</v>
       </c>
       <c r="C34">
-        <v>3315</v>
+        <v>540</v>
       </c>
       <c r="D34">
-        <v>11959</v>
+        <v>77044</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.45300000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>46232</v>
+        <v>46265</v>
       </c>
       <c r="B35">
-        <v>21.76</v>
+        <v>70.83</v>
       </c>
       <c r="C35">
-        <v>3150</v>
+        <v>543</v>
       </c>
       <c r="D35">
-        <v>16174</v>
-      </c>
+        <v>191074</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B36">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="C36">
+        <v>518</v>
+      </c>
+      <c r="D36">
+        <v>82818</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.48599999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B37">
+        <v>75.44</v>
+      </c>
+      <c r="C37">
+        <v>518</v>
+      </c>
+      <c r="D37">
+        <v>52916</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0.248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B38">
+        <v>69.98</v>
+      </c>
+      <c r="C38">
+        <v>477.5</v>
+      </c>
+      <c r="D38">
+        <v>123833</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.442</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B39">
+        <v>72.040000000000006</v>
+      </c>
+      <c r="C39">
+        <v>496</v>
+      </c>
+      <c r="D39">
+        <v>75119</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B40">
+        <v>87.24</v>
+      </c>
+      <c r="C40">
+        <v>517</v>
+      </c>
+      <c r="D40">
+        <v>57089</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.27600000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B41">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="C41">
+        <v>531</v>
+      </c>
+      <c r="D41">
+        <v>76221</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.55500000000000005</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B42">
+        <v>80.42</v>
+      </c>
+      <c r="C42">
+        <v>523</v>
+      </c>
+      <c r="D42">
+        <v>37518</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B43">
+        <v>67.540000000000006</v>
+      </c>
+      <c r="C43">
+        <v>515</v>
+      </c>
+      <c r="D43">
+        <v>38162</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.41599999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B44">
+        <v>60.79</v>
+      </c>
+      <c r="C44">
+        <v>493</v>
+      </c>
+      <c r="D44">
+        <v>38482</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.41399999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B45">
+        <v>53.93</v>
+      </c>
+      <c r="C45">
+        <v>473</v>
+      </c>
+      <c r="D45">
+        <v>49215</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0.47599999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B46">
+        <v>49.52</v>
+      </c>
+      <c r="C46">
+        <v>465.5</v>
+      </c>
+      <c r="D46">
+        <v>34239</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0.44400000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B47">
+        <v>62.22</v>
+      </c>
+      <c r="C47">
+        <v>492.5</v>
+      </c>
+      <c r="D47">
+        <v>36437</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0.57899999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B48">
+        <v>73.08</v>
+      </c>
+      <c r="C48">
+        <v>488</v>
+      </c>
+      <c r="D48">
+        <v>44996</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0.52600000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B49">
+        <v>89.57</v>
+      </c>
+      <c r="C49">
+        <v>525</v>
+      </c>
+      <c r="D49">
+        <v>79513</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0.52900000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="4b5cace2-6bdb-4302-bf8d-1de49c0887c5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101004C70BD0EF888DB4A8AEB033AC6A6FDFD" ma:contentTypeVersion="8" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="daff39ad397c726b98f38988a6ba4be8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="4b5cace2-6bdb-4302-bf8d-1de49c0887c5" xmlns:ns4="9dba4127-55c1-4f18-b326-aa805e3ab068" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="090fd4666f8b1c2fbefc185fbcdb6ac0" ns3:_="" ns4:_="">
     <xsd:import namespace="4b5cace2-6bdb-4302-bf8d-1de49c0887c5"/>
@@ -6650,7 +13352,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6659,24 +13361,15 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1101D1-6552-43E3-AFC8-73E55E621986}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="4b5cace2-6bdb-4302-bf8d-1de49c0887c5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9dba4127-55c1-4f18-b326-aa805e3ab068"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="4b5cace2-6bdb-4302-bf8d-1de49c0887c5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D839321-C70C-48AB-A057-112201BFF419}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6695,10 +13388,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F0C9D8D-D9C2-4FFE-B72E-DBE4E7B229B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1101D1-6552-43E3-AFC8-73E55E621986}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="4b5cace2-6bdb-4302-bf8d-1de49c0887c5"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dba4127-55c1-4f18-b326-aa805e3ab068"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>